--- a/Data/compiled_article_data.xlsx
+++ b/Data/compiled_article_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,256 +463,23 @@
           <t>source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BOCK CO2 Compressors Found to Vibrate Less at Ohio Supermarket</t>
+          <t>Frascold’s New NEXUS Screw Compressor for High-Temperature Heat Pump Applications Can Work With Butane and Isopentane</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
-        <is>
-          <t>In a new whitepaper, Danish component manufacturer Danfoss reported that its BOCK HGX series CO2 (R744) compressors experienced an average of 83% less vibration compared to legacy compressors in a test retrofit installation at a supermarket in Ohio.
-The whitepaper – “Danfoss BOCK CO₂ Compressor Reduces Vibration for Optimal Transcritical Supermarket Refrigeration Performance” – is available here.
-Using a calibrated vibration meter, Danfoss application engineers captured measurements at multiple locations on the rack and at various points on individual compressors and common piping lines.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>46069</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>In a new whitepaper, Danish component manufacturer Danfoss reported that its BOCK HGX series CO2 (R744) compressors experienced an average of 83% less vibration compared to legacy compressors in a test retrofit installation at a supermarket in Ohio.
-The whitepaper – “Danfoss BOCK CO₂ Compressor Reduces Vibration for Optimal Transcritical Supermarket Refrigeration Performance” – is available here.
-Using a calibrated vibration meter, Danfoss application engineers captured measurements at multiple locations on the rack and at various points on individual compressors and common piping lines.
-Compared to existing CO2 compressors, the BOCK units achieved vibration reductions ranging from 48.3% to 97.7% at various points and capacities, the whitepaper said.
-In addition, the BOCK lead compressor employing a variable frequency drive (VFD) achieved a wider frequency range – from 35–70Hz compared to the original compressor’s 40-60Hz range – resulting in a larger capacity range in the suction group without added vibration,” it said.
-Abnormal vibration
-The Ohio supermarket had been experiencing “abnormal, excessive compressor and rack vibration” in its legacy transcritical CO2 system, said the whitepaper. It added that excessive vibration is “one of the most persistent CO2 compressor reliability challenges,” causing damage to racks, piping and structural components and resulting in reduced compression cycle effectiveness and excess energy consumption.
-“We are encouraged by the test results that affirmed the operational and sustainability benefits of BOCK compressors for transcritical CO2 refrigeration systems,” said Chris Brown, Application Engineering Manager at Danfoss, in a statement. “Danfoss BOCK HGX compressors can deliver the energy savings and environmental benefits of CO2 safely and reliably in a wide range of supermarket refrigeration sites, removing a critical barrier to increased adoption of CO2 across the industry.”
-“We are encouraged by the test results that affirmed the operational and sustainability benefits of BOCK compressors for transcritical CO2 refrigeration systems.”
-Chris Brown, Danfoss
-In the test case, seven Danfoss BOCK HGX series compressors were employed in a transcritical system. All compressors were semi-hermetic and were charged with a synthetic refrigeration oil based on special polyolesters for use with CO2 in transcritical applications. The refrigeration rack supplied a total of 1,121kBTUh (93.4TR/328,5kW) of cooling.
-“The vibration reductions also resulted in less noise and less shaking of the pipes and other rack components,” Danfoss said. “In addition to the improvements in safety and reliability of the operating components, the environment of the area was much more pleasant for maintenance personnel.”
-Danfoss’s BOCK HGX56 CO2T six-cylinder semi-hermetic compressor was named the winner in the refrigeration category of the 2025 AHR Expo Innovation Award.
-Danfoss finalized its acquisition of CO2 compressor manufacturer BOCK from NORD Holding in March 2023.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/bock-co2-compressors-found-to-vibrate-less-at-ohio-supermarket/</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Advansor Launches ‘Enhanced’ CuBig II With 50% More Cooling and Heating Capacity</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Danish manufacturer Advansor, part of the Dover Corporation, has announced an “enhanced” version of its CO2 (R744)-based CuBig II that offers 50% more cooling and heating capacity.
-The CuBig II offers cooling, freezing, heating and air-conditioning all in one package, with the update pushing the unit’s medium-temperature (MT) capacity from 400 to 600kW (113 to 170TR) and its heating capacity from 650 to 850kW (184 to 241TR). In addition, Advansor said that the low-temperature (LT) performance has been optimized to “ensure stability under higher MT loads.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>46066</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Danish manufacturer Advansor, part of the Dover Corporation, has announced an “enhanced” version of its CO2 (R744)-based CuBig II that offers 50% more cooling and heating capacity.
-The CuBig II offers cooling, freezing, heating and air-conditioning all in one package, with the update pushing the unit’s medium-temperature (MT) capacity from 400 to 600kW (113 to 170TR) and its heating capacity from 650 to 850kW (184 to 241TR). In addition, Advansor said that the low-temperature (LT) performance has been optimized to “ensure stability under higher MT loads.”
-“The LT capacity no longer drops as aggressively, which means improved simultaneous cooling for MT and LT circuits,” said Kenneth Madsen, CTO of Advansor, in a press release. “The wider operating envelope supports more diverse load combinations, reducing design constraints and improving adaptability.”
-The CuBig II is designed for large supermarkets and cold storage facilities and is also “ideal” as a heat pump for commercial and industrial applications, according to Advansor.
-Additional details: The CuBig II has a maximum low-temperature capacity of 330kW (93TR), a maximum air-conditioning capacity of 180kW (51TR) and a maximum heat recovery capacity of 850kW.
-Product evolutions: In addition to the CuBig II update, Advansor has also released new versions of its CO2-based ValuePack and Steel XL rack in the past year.
-Advansor launched a new version of its SteelXL rack in January 2025 with a maximum cooling capacity of 2.7MW (767TR), 1.9MW (540TR) of freezing, up to 4MW (1,137TR) of heating and 0.5MW (142TR) of air-conditioning, all on one frame.
-That same month the company launched an upgrade of its ValuePack refrigeration unit, raising the standard operating pressure to 130bar (1,885psi) from 120bar (1,740psi). The enhancement was designed to facilitate higher cooling capacities and improve operational efficiency and safety, according to Advansor, while also enabling the unit to be used for cold storage and light industrial applications, in addition to food retail.
-Quotable: “The larger capacity range often correlates with optimized compressor staging and reduced energy consumption per kW delivered,” said Madsen. “All of this gives our customers greater flexibility and performance.”</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/advansor-launches-enhanced-cubig-ii-with-50-more-cooling-and-heating-capacity/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Johnson Controls Introduces Air-to-Water Reversible York YAS R290 Heat Pump Models to the European Market</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Johnson Controls is introducing its air-to-water reversible York-brand YAS propane (R290) heat pump models to the European market, offering configurations that can supply cooling, heating or simultaneous cooling and heating, and deliver up to 65/77°C (149/171°F) hot water, depending on the model.
-Using scroll compressor technology and axial fans, the three models ‒ YAS SC WP, YAS SC WP WA and YAS SC GPS ‒ operate in ambient temperatures as low as −20°C (−4°F). The units, which use 6.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>46065</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Johnson Controls is introducing its air-to-water reversible York-brand YAS propane (R290) heat pump models to the European market, offering configurations that can supply cooling, heating or simultaneous cooling and heating, and deliver up to 65/77°C (149/171°F) hot water, depending on the model.
-Using scroll compressor technology and axial fans, the three models ‒ YAS SC WP, YAS SC WP WA and YAS SC GPS ‒ operate in ambient temperatures as low as −20°C (−4°F). The units, which use 6.1 or 8.1kg of propane, offer heating capacities ranging from 86.7 to 139kW (24.7 to 39.5TR) and cooling capacities from 66.3 to 110kW (18.9 to 31.3TR), supporting residential, commercial and industrial applications, according to Johnson Controls.
-“The scroll compressors with orbiting spirals are optimized for heat pump operation at high compression ratios,” Johnson Controls said. “Depending on the model, the [compressors] are arranged in tandem or trio configuration and paired with electronically controlled air flow on the source side, which enables excellent seasonal efficiency ratios.”
-Either/or units: Two of the YAS models produce heating or cooling, with one version optimized for colder climates and the other one for higher ambient temperature conditions.
-The YAS SC WP model for colder climates offers heating capacities from 88.9 to 112kW (25.3 to 31.8TR), with a SCOP of up to 4.29, and cooling capacities from 66.3 to 89.2kW (18.9 to 25.4TR), with an EER of up to 2.51.
-The wide ambient model YAS SC WP WA offers 88.2kW (25.1TR) of heating capacity, with a SCOP of up to 3.77, and 105kW (29.9TR) of cooling capacity, with an EER of up to 3.55.
-Simultaneous unit: The YAS SC GPS model offers three operation modes: cooling, heating or cooling with heating.
-When operating solely for chilling, the unit offers cooling capacities ranging from 72.1 to 99.1kW (20.5 to 28.2TR), with an EER of up to 2.73.
-When operating solely for heat, the unit offers heating capacities ranging from 86.7 to 116kW (24.7 to 33TR), with a COP of up to 3.92.
-In simultaneous mode, the unit offers cooling capacities ranging from 79.5 to 110kW (22.6 to 31.3TR) and heating capacities ranging from 101 to 139kW (28.7 to 39.5TR), with a total efficiency ratio of up to 8.68.
-Australian application: In 2024 Johnson Controls received compliance certification from the Queensland Resources, Safety and Health (RSH) statutory board for its York-brand YAS large-scale propane chillers and air-to-water heat pumps.
-Working with local officials, the manufacturer replaced the existing HFC air-conditioning unit in a Windsor shopping center with two roughly 300kW (85TR)-capacity R290 chillers, according to Rickey Du, Product and Technology Manager of Industrial Refrigeration at Johnson Controls for Australia and New Zealand.
-Installed in August 2024, the project became Queensland’s “first” approved propane chiller deployment, according to Du, with final regulatory approval granted in December 2024.
-Quotable: “Every unit is fully assembled and factory tested [and] supplied with the appropriate refrigerant and non-freezing oil charge,” Johnson Controls said. “As a result, installation only requires positioning the equipment and connecting it to the hydraulic and electrical supply lines.”
-“The scroll compressors with orbiting spirals are optimized for heat pump operation at high compression ratios.”
-Johnson Controls</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/johnson-controls-introduces-air-to-water-reversible-york-yas-r290-heat-pump-models-to-the-european-market/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EU Launches €1.8 Million Heat Pump Subscription Model for Leased Commercial and Public Buildings</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The EU has launched a €1.8 million ($2.15 million) subscription model, funded through its LIFE Program from November 2025 to October 2028, to encourage the adoption of heat pumps in leased commercial and public buildings.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>46076</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>The EU has launched a €1.8 million ($2.15 million) subscription model, funded through its LIFE Program from November 2025 to October 2028, to encourage the adoption of heat pumps in leased commercial and public buildings.
-The HP-Subscribe model uses third-party ownership and subscription fees to address barriers to heat pump installations in leased buildings caused by the split incentive between landlords and tenants. Hydrocarbon natural refrigerant heat pumps are eligible under the EU LIFE Program and compliant with the EU F-gas Regulation’s low-GWP requirements.
-“With HP-Subscribe, we want to make clean heating accessible to every building, regardless of ownership structure or financial capacity,” said Petra Pomper, Project Coordinator and building sector expert at the Institute for European Energy and Climate Policy (IEECP). “This project demonstrates that the energy transition can advance in a way that is fair, scalable and effective.”
-Heat pumps offer a carbon-neutral alternative to fossil fuels for heating and cooling, aligning with goals outlined in the European Green Deal and the REPowerEU plan, according to the European Commission. In 2024 heat pumps claimed 28% of the region’s space heating market, according to the European Heat Pump Association (EHPA).
-Based on the size of the leased building, the required capacities for cooling, heating and hot water could range from a few kilowatts to more than a megawatt. In the past, landlords shouldered the financial burden of installing and maintaining heat pumps, while tenants paid lower energy bills.
-How HP-Subscribe works: The model shifts heat pump ownership, installation and maintenance to a service provider, a third party separate from the landlord or tenant. To spread the initial cost of the heat pump over time, end users pay a subscription fee.
-HP-Subscribe aims to engage energy-service companies, financial institutions, public authorities, building owners and manufacturers to validate and promote the model, with pilot projects in Austria, France and Greece, the European Commission said.
-In Ireland the project will connect existing heat pump initiatives with service providers and financial partners, according to EHPA.
-The project will enhance the business case for heat pumps by leveraging regulatory frameworks such as white certificate schemes and demand–response programs that support grid flexibility.
-Many options: Several European manufacturers offer propane (R290)-based heat pump solutions that meet the requirements of the model.
-Procure Plus appointed four R290 heat pumps produced by Viessmann Climate Solutions, a division EUof Carrier Global Corporation, to the U.K. social housing and other public sector low- and zero-carbon projects framework. The capacities of the units range from 1.1 to 140kW (0.6 to 39.8TR).
-Italian Enerblue’s Purple range of air-to-water heat pumps offers heating capacities of 22–221kW (6.3–62.8TR). Its new Palladium range includes a four-pipe model capable of providing simultaneous heating and cooling.
-In September 2025 Panasonic announced that it was investing €320 million ($373.8 million) to expand and refurbish its facility in the Czech Republic, with the aim of producing 1.4 million residential and commercial heat pumps for the European market by 2030.
-Cooling projects: The EU continues to finance the development of sustainable solutions as part of its climate action plan.
-The Life-ZeroGWP Project, coordinated by Italian Innova, developed the first high-efficiency double-ducted propane air conditioner without an outdoor unit. With less than 150g of R290 per circuit, the resulting INNOVA 2.0NR, available from 2022, compares to the best HFC solutions on the market in terms of energy efficiency and convenience, according to Life-ZeroGWP.
-The SMACool project, which runs until September 2027 with an allotted €3.9 million ($4.45 million) in funding, aims to develop a prototype of a residential air conditioner using elastocaloric technology. Instead of a refrigerant, it uses nickel-titanium, also known as nitinol, which heats up when mechanically stressed and cools when de-stressed.
-Quotable: “This subscription–based service guarantees modern, efficient and clean heating with reduced energy costs for tenants, while owners benefit from higher building value without the burden of capital investment,” EHPA said.
-“With HP-Subscribe, we want to make clean heating accessible to every building, regardless of ownership structure or financial capacity.”
-Petra Pomper, HP-Subscribe Project Coordinator</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/eu-launches-e1-8-million-heat-pump-subscription-model-for-leased-commercial-and-public-buildings/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HVAC&amp;R Japan 2026: JEXSYS Launches 130°C High-Temperature Hot Water CO2 Heat Pump</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>JEXSYS, formerly known as Nihon Netsugen Systems, has launched a high-temperature CO2 (R744) heat pump for the Asia–Pacific region capable of producing up to 130°C (266°F) pressurized hot water for industrial processing applications.
-The standard unit offers a heating capacity of 500kW (142.2TR) with a COP of 4.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>46064</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>JEXSYS, formerly known as Nihon Netsugen Systems, has launched a high-temperature CO2 (R744) heat pump for the Asia–Pacific region capable of producing up to 130°C (266°F) pressurized hot water for industrial processing applications.
-The standard unit offers a heating capacity of 500kW (142.2TR) with a COP of 4.8. However, JEXSYS has the flexibility to manufacture larger capacities depending on a client’s needs, Katsuhiko Harada, the company’s President, told NaturalRefrigerants.com at the HVAC&amp;R Japan 2026 show. The event, held January 27‒30 in Tokyo, was organized by the The Japan Refrigeration and Air Conditioning Industry Association.
-“Our industrial refrigeration customers always have a boiler to meet the food and beverage industry’s requirement for 120‒130°C [248‒266°F] sanitary hot water,” Harada said. “Boilers cause a headache for two reasons: the price of fossil fuel is going up and really high CO2e emissions. Therefore, I think introducing a CO2 heat pump in the Japanese market is very important.”
-Development/reaction: To replace boilers in the food/beverage industry, JEXSYS first attempted to promote its ammonia (R717) heat pump. However, it did not meet the industry’s needs, with hot water temperatures topping out around 80‒90°C (176‒194°F), according to Harada.
-Drawing on its experience producing CO2 refrigeration equipment, JEXSYS spent a year developing a CO2 heat pump with the aim of producing 130°C pressurized hot water ‒ a goal it achieved at the end of 2025.
-The unit produces 4.2 metric tons of hot water per hour for industrial applications requiring temperatures above 100°C (212°F), including heating and melting of raw materials, sterilization, cleaning and drying.
-Although the main purpose of the unit is heating, it also produces cold water, according to Harada, making it eligible for the Japanese government’s subsidy schemes for heat recovery in the food industry.
-Gaining experience: JEXSYS launched its first CO2 condensing units in 2015, with early sales catered to small, privately owned cold storage companies.
-“So far we’ve installed 760 CO2 units in 240 completed projects,” Harada said, adding that the company’s docket for the next two years includes providing CO2 refrigeration units for “big” logistic centers owned by real estate-investing companies.
-It has CO2 equipment operating in Malaysia and the Philippines. Its five-year-old installation in Malaysia supplies fantastic energy savings with no reliability issues, Harada said.
-In 2023 the manufacturer opened a new factory in Shiga, Japan, which doubled its CO2 equipment-production capacity to meet the growing year-on-year demand.
-Business strategy: Looking ahead, Harada believes CO2 refrigeration and cooling will eventually mature and reach a growth ceiling, making it necessary for JEXSYS to develop a new business to sustain long-term growth.
-Entering the heating market with a CO2 heat pump aligns with the manufacturer’s growth strategy.
-“We expect this new business area to grow in the future, just as CO2 refrigeration has,” Harada said.
-Quotable: “We’ve been talking to several potential customers about a high-temperature CO2 heat pump for two or three years,” Harada said. “They are waiting for this launch,” he added, indicating that JEXSYS expects to sell 10 units in 2026.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/hvacr-japan-2026-jexsys-launches-130c-high-temperature-hot-water-co2-heat-pump/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Frascold’s New NEXUS Screw Compressor for High-Temperature Heat Pump Applications Can Work With Butane and Isopentane</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
         <is>
           <t>Italian manufacturer Frascold has launched its new generation of NEXUS semi-hermetic screw compressors for high-temperature heat pumps, which are compatible with hydrocarbon refrigerants, including butane (R600) and isopentane (R601a).
 The NEXUS screw compressors have a maximum operating temperature of 140°C (284°F) and a heating capacity of over 1MW (284TR), with volumetric displacements from 316 to 912m³/h (186 to 537CFM) at 50Hz and motors up to 300HP. They are designed to work in air-to-water and water-to-water configurations with butane and isopentane.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C2" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Italian manufacturer Frascold has launched its new generation of NEXUS semi-hermetic screw compressors for high-temperature heat pumps, which are compatible with hydrocarbon refrigerants, including butane (R600) and isopentane (R601a).
 The NEXUS screw compressors have a maximum operating temperature of 140°C (284°F) and a heating capacity of over 1MW (284TR), with volumetric displacements from 316 to 912m³/h (186 to 537CFM) at 50Hz and motors up to 300HP. They are designed to work in air-to-water and water-to-water configurations with butane and isopentane. In addition to hydrocarbons, the compressor is also compatible with R1233zd.
@@ -724,299 +491,32 @@
 The ATEX-HT semi-hermetic reciprocating compressor features a line start permanent magnet (LSPM) electric motor that increases efficiency by 6% compared to a standard asynchronous motor, according to Tecnofreddo. LSPM motors start like induction motors but have permanent magnets on the rotor to eliminate slip – the lag between the stator and rotor – that leads to energy loss.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>https://naturalrefrigerants.com/news/frascolds-new-nexus-screw-compressor-for-high-temperature-heat-pump-applications-can-work-with-butane-and-isopentane/</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cencosud, Nestlé and OXXO Colombia to Present at ATMO LATAM 2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ATMOsphere, publisher of NaturalRefrigerants.com, has published a preview of the program for ATMOsphere (ATMO) LATAM 2026, which will feature a keynote from leading South America retailer Cencosud as well as presentations from Nestlé and OXXO Colombia, among other end users.
-Cencosud’s Sustainability Manager will kick off ATMO LATAM 2026, set for March 9–10 in Bogotá, by sharing the company’s vision for sustainability and its progress in adopting natural refrigerants.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>46062</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ATMOsphere, publisher of NaturalRefrigerants.com, has published a preview of the program for ATMOsphere (ATMO) LATAM 2026, which will feature a keynote from leading South America retailer Cencosud as well as presentations from Nestlé and OXXO Colombia, among other end users.
-Cencosud’s Sustainability Manager will kick off ATMO LATAM 2026, set for March 9–10 in Bogotá, by sharing the company’s vision for sustainability and its progress in adopting natural refrigerants. The company operates more than 1,000 supermarkets and has made the “conversion of refrigerant gases” one of its sustainability priorities. It operates 15 stores that use transcritical CO2 (R744) refrigeration systems, according to its 2024 sustainability report.
-Nestlé and contractor Sistemas de Refrigeración Totales will present a critical load ammonia (R717) chiller with adiabatic condensers. OXXO Colombia, Latin America’s largest convenience store chain, will speak on the same panel about its work with natural refrigerants. 
-End users from the agricultural sector will also take the stage at ATMO LATAM 2026. Avo Pak, a Colombian avocado processor, will speak about its use of CO2 refrigeration systems. The joint presentation will also feature contractor SUTRAK and manufacturer Advansor. 
-Contractors and installers will have their own dedicated panel where they will share their experiences with natural refrigerants and outlook on the sector. Chilean contractor Sofrisur and Costa Rican contractor Dicoma Refrigeración are two of the confirmed presenters.
-Get Your Tickets to ATMO LATAM 2026
-Policy and training
-Day two will feature a policy panel covering standards and regulations impacting natural refrigerants in Latin America. It will feature Edwin M. Dickson, Environmental Consultant at Colombia’s Ministry of Environment and Sustainable Development, and Omarly Acevedo, International Consultant, Montreal Protocol and for UNIDO in Latin America. ATMOsphere will also discuss HFOs and the growing threat of PFAS (per- and polyfluoroalkyl substances) and TFA (trifluoroacetic acid).
-Training will also be a topic of discussion on day two of ATMO LATAM. ACAIRE (The Colombian Association of Air-Conditioning and Refrigeration), will headline the training panel with additional participants announced soon. The session will bring together experts to discuss the current state, opportunities and challenges of professional training in natural refrigerants in Latin America.
-The program is still being finalized and will also include sessions dedicated to global and regional market trends. Tickets for ATMO LATAM 2026 are still available and can be purchased here.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/cencosud-nestle-and-oxxo-colombia-to-present-at-atmo-latam-2026/</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HYTING Commissions ‘World’s First’ Customer-Installed Catalytic Hydrogen Air-Heating System</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HYTING, a German manufacturer of hydrogen-based heating solutions, has commissioned what it describes as the “world’s first” customer-installed catalytic hydrogen air-heating system in a new industrial facility in Offenbach, Germany.
-Paired with a heat pump, the 10kW (2.8TR) capacity catalytic unit supports the client’s peak heating demand, including in low ambient temperatures, using hydrogen supplied locally, according to HYTING.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HYTING, a German manufacturer of hydrogen-based heating solutions, has commissioned what it describes as the “world’s first” customer-installed catalytic hydrogen air-heating system in a new industrial facility in Offenbach, Germany.
-Paired with a heat pump, the 10kW (2.8TR) capacity catalytic unit supports the client’s peak heating demand, including in low ambient temperatures, using hydrogen supplied locally, according to HYTING. Flusys, a producer of pumps and fluid systems for industrial applications, installed the hybrid system to heat a 1,000m3 (35,300ft3) production space.
-The catalytic unit engages based on the hybrid setup’s optimum operating cost, HYTING told NaturalRefrigerants.com. The switch-on point depends on the heat pump’s efficiency and the relative cost of electricity versus the cost of hydrogen.
-“Our vision has always been to see hydrogen replace fossil fuels and make an invaluable contribution to decarbonizing the heating sector,” said Tim Hannig, Founder and Managing Director of HYTING. “Our technology is simple, safe, efficient and clean.”
-Applications for the catalytic hydrogen technology include commercial and industrial building HVAC, up to 300°C (572°F) process heating and auxiliary heating for the automotive sector, according to HYTING. Initially the units will come in heating capacities of 10 or 50kW (2.8 or 14.2TR), with higher capacity requirements met through modular configurations. HYTING, founded in 2021, said that it is scaling the unit for series production, with another customer installation scheduled for the first quarter of 2026.
-The technology: Rather than using flame-based combustion to generate heat, the process uses a catalytic chemical reaction. The technology produces no carbon emissions, nitrogen oxides or particulate matter, with water vapor as the only by-product.
-A controlled mixture of hydrogen and oxygen from the ambient air flows over HYTING’s proprietary catalyst surface, where it undergoes rapid oxidation, which generates heat.
-HYTING states that the unit is inherently safe, with hydrogen kept outside the catalyst zone in uncontrolled or hazardous concentrations.
-The technology, suitable for new installations and retrofits, can be combined with “any heat source,” the company said.
-Validation/certification: Durability testing, conducted by an independent engineering service provider, simulated 10 years of real-world operation, according to HYTING.
-The unit completed 2,500 hours of testing without failure or measurable wear on critical safety components.
-HYTING’s catalytic hydrogen technology is EU Gas Appliance Regulation-certified, indicating that it meets the safety, health and environmental requirements for gas-fired appliances.
-Optimizing systems: “Peak heating installations for commercial and industrial buildings can save customers costs from day one by drastically reducing capacity and demand charges and overall system costs,” HYTING said.
-Compared to installing a heat pump sized to meet peak demands, the hybrid setup can deliver up to 30% lower capital costs and up to 20% lower operating costs, depending on the price of hydrogen and the operating strategy, the company told NaturalRefrigerants.com.
-A simple retrofit solution can start around €20,000 ($23,600), HYTING said, with CAPEX costs based on project-specific requirements, including capacity and scope.
-Quotable: “The Flusys’ installation will prove not only the efficacy of HYTING’s technology but also demonstrate that hydrogen can replace natural gas as a cleaner, more sustainable source of heating,” the company said.
-“Our vision has always been to see hydrogen replace fossil fuels and make an invaluable contribution to decarbonizing the heating sector.”
-Tim Hannig, Founder and Managing Director of HYTING</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/hyting-commissions-worlds-first-customer-installed-catalytic-hydrogen-air-heating-system/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Part 2: BAC’s Heat Rejection and Single-Phase Immersion Technology Provide ‘End-to-End’ Cooling Solution for Data Centers</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Part 1: BAC’s Heat Rejection and Single-Phase Immersion Technology Provide ‘End-to-End’ Cooling Solution for Data Centers</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>This is an excerpt from an article featured in ATMOsphere’s “Clean Cooling for Data Centers 2025” report, which can be downloaded here. ATMOsphere is the publisher of NaturalRefrigerants.com.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>46071</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>This is an excerpt from an article featured in ATMOsphere’s “Clean Cooling for Data Centers 2025” report, which can be downloaded here. ATMOsphere is the publisher of NaturalRefrigerants.com.
-BAC’s COBALT immersion cooling system can be found in action at Skybox Houston One, an HPC data center in Houston, Texas, with 4MW of installed IT power capacity. Operational since 2019,  the facility runs entirely on renewable energy and operates in 100% free-cooling mode year-round despite the notoriously hot and humid climate.
-The system features more than 300 26U-wide immersion tanks, each housing 13 high-density servers submerged in dielectric fluid. These tanks are connected to a closed-loop cooling water circuit served by six BAC evaporative cooling towers for heat rejection and five pump sets that circulate water between the tanks and towers. Within the data hall, four computer room air-conditioning (CRAC) units provide limited, non-mission-critical comfort cooling.
-The use of BAC’s immersion cooling technology substantially reduces the data center’s energy use compared to a setup using CRAHs (computer room air handlers) – which supply cool air to the server room via air-cooled chillers – according to Jan Tysebaert, Global General Manager for Data Center Cooling at BAC. IT power consumption was reduced by 20% as server fans were no longer required.
-Combined with the use of free evaporative cooling – rather than mechanical cooling – and a streamlined system architecture, total energy savings reached around 80% for the cooling system and approximately 30% at the overall facility level.
-The Skybox Houston One data center. Photo credit: Skybox
-PUE vs. TUE
-While most facilities report power usage effectiveness (PUE) as their primary efficiency metric, BAC also highlights total-power usage effectiveness (TUE), which is defined as the ratio of total facility load to compute load.
-“PUE looks at the facility, but it does not look at the efficiency of the IT hardware,” Tysebaert noted. “It does not do justice to liquid-cooled facilities.”
-PUE does not account for the effect of lowering IT load – such as by eliminating the need for server fans – and can therefore make a more efficient data center appear to have a higher PUE. For Skybox Houston One, the immersion and evaporative cooling configuration achieves a TUE of approximately 1.15 compared to 1.60 for a setup using air-cooled chillers and CRAHs.
-Beyond efficiency, the approach adopted at SkyBox Houston One is “extremely simple” in design, resulting in low upfront costs and enabling easy scaling, Tysebaert said. It can work with any type of server and at higher process fluid temperatures, he noted. By integrating the immersion tanks directly with the facility’s evaporative cooling system, BAC’s design also reduces the data hall footprint, enabling operators to maximize compute density within the same physical space.
-“It’s actually unbelievable [that] we’re not doing this for all other data centers worldwide already,” Tysebaert said.
-“PUE looks at the facility, but it does not look at the efficiency of the IT hardware,” Tysebaert noted. “It does not do justice to liquid-cooled facilities.”
-Jan Tysebaert, 
-Global General Manager for Data Center Cooling at BAC</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/part-2-bacs-heat-rejection-and-single-phase-immersion-technology-provide-end-to-end-cooling-solution-for-data-centers/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Brazil HVAC&amp;R Association Presents Proposed Strategy for First Phase of National HFC Reduction Program</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>The Brazilian Association of Refrigeration, Air Conditioning, Ventilation and Heating (ABRAVA) has presented a proposed strategy for the first phase of Brazil’s national program to reduce the consumption of HFCs.
-The first phase of the Brazilian Program for Reducing the Consumption of HFCs (HFCs Program) will run from 2027 to 2032 and aims to cut national HFC consumption by 10% by 2029 – equivalent to approximately 7.3 million metric tons of CO2e.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>46059</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The Brazilian Association of Refrigeration, Air Conditioning, Ventilation and Heating (ABRAVA) has presented a proposed strategy for the first phase of Brazil’s national program to reduce the consumption of HFCs.
-The first phase of the Brazilian Program for Reducing the Consumption of HFCs (HFCs Program) will run from 2027 to 2032 and aims to cut national HFC consumption by 10% by 2029 – equivalent to approximately 7.3 million metric tons of CO2e. This target aligns with Brazil’s commitments under the Kigali Amendment to the Montreal Protocol, which the country ratified in October 2022.
-The proposed strategy centers on a package of regulatory measures designed to support Brazil’s transition to low-GWP and energy-efficient refrigerants across multiple sectors, including natural refrigerant training for technicians. In addition to commercial refrigeration and air-conditioning, the strategy covers mobile air-conditioning (MAC), data centers, industrial refrigeration and heat pumps.
-“The active participation of different sectors is essential to ensure that public policies reflect the real needs of the market and society,” said Frank Amorim, Technical Representative of Brazil’s Ministry of Environment and Climate Change (MMA). “More than a set of actions, this is a comprehensive study on the consumption of these gases in various sectors in Brazil, offering a solid basis for the technological and energy transition.”
-The proposed strategy was presented at a meeting held in São Paulo on December 1, organized by the MMA in partnership with the United Nations Development Programme (UNDP), the United Nations Industrial Development Organization (UNIDO) and Germany’s development agency, the GIZ (German Agency for International Cooperation).
-The MMA is accepting public feedback on the proposed strategy for the first phase of the HFCs Program through December 27.
-“More than a set of actions, this is a comprehensive study on the consumption of these gases in various sectors in Brazil, offering a solid basis for the technological and energy transition.”
-Frank Amorim, Technical Representative of Brazil’s Ministry of Environment and Climate Change
-Curbing rising consumption
-Without additional action, Brazil’s HFC consumption could reach 55 million metric tons of CO2e by 2035, surpassing its allocated limit of 51 million metric tons under the Kigali Amendment, according to Ana Paula Leal, Project Coordinator for UNDP. The HFCs Program is intended to ensure compliance with these international obligations.
-Proposed measures include establishing maximum GWP limits by equipment type and/or sector, banning the use of R134a and R410A in residential refrigerators and air conditioners starting in 2029 and implementing mandatory energy-efficiency labeling for refrigeration and air-conditioning equipment. The strategy also highlights the need for sector-specific policies for supermarkets to support a safe and economically viable transition to low-GWP and energy-efficient refrigerants, as well as the internalization of international HVAC&amp;R standards.
-Capacity building is also a core component of the proposed strategy, with plans to launch a Qualification, Certification and Registration project, which will develop and test a system for expanding and upskilling Brazil’s HVAC&amp;R workforce. The strategy also includes additional technician training focused on the safe and efficient use of natural refrigerants, as well as a project for mandatory refrigerant handling and maintenance practices in the MAC sector.
-These training efforts will build on progress achieved under Brazil’s HCFC Elimination Program (PBH), according to Stefanie von Heinemann, Consultant and Project Manager for the GIZ.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/brazil-hvacr-association-presents-proposed-strategy-for-first-phase-of-national-hfc-reduction-program/</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Epta Completes Its Acquisition of Hauser</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Epta announced on February 17 that it has completed its acquisition of Hauser, with the deal increasing the Epta Group’s revenues to more than €2 billion ($2.3 billion) annually and its headcount to more than 10,000 employees.
-The multinational manufacturer of commercial refrigeration equipment announced its acquisition of Hauser, an Austrian manufacturer of self-contained and remote refrigeration cabinets and industrial refrigeration systems, in July 2025.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Epta announced on February 17 that it has completed its acquisition of Hauser, with the deal increasing the Epta Group’s revenues to more than €2 billion ($2.3 billion) annually and its headcount to more than 10,000 employees.
-The multinational manufacturer of commercial refrigeration equipment announced its acquisition of Hauser, an Austrian manufacturer of self-contained and remote refrigeration cabinets and industrial refrigeration systems, in July 2025. It said at the time that the goal of the deal is “to enhance [the] Epta Group’s presence and competitiveness in the retail sector.” Hauser operates two plants, one in Austria and one in the Czech Republic.
-“This operation marks a key milestone in Epta’s long-term strategy,” said Marco Nocivelli, CEO of Epta, in a press release. “By combining competencies, technologies and scale, we significantly enhance our ability to drive sustainable and digital innovation. The acquisition of Hauser further strengthens our offering along the full value chain and consolidates our leadership in natural refrigeration and energy-efficient solutions.”
-Epta and Hauser both manufacture commercial refrigeration equipment, including plug-in propane (R290) cases, remote CO2 (R744) cases and CO2 racks. Hauser also manufactures industrial refrigeration systems using CO2, ammonia (R717) and synthetic refrigerants.
-“Joining Epta marks a pivotal moment for our company,” said Thomas Loibl, CEO of Hauser, in a press release. “With a global partner that shares our core values, Hauser is well positioned to further consolidate its footprint while continuing to deliver long- term value to customers.”
-Epta told NaturalRefrigerants.com in July 2025 that it is “actively evaluating further expansion opportunities,” specifically new acquisitions/partnerships in Asia and North America.
-“The acquisition of Hauser further strengthens our offering along the full value chain and consolidates our leadership in natural refrigeration and energy-efficient solutions.”
-Marco Nocivelli, 
-CEO of Epta</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/epta-completes-its-acquisition-of-hauser/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Part 2: Why Penta Infra Chose Secon’s R290 Chillers for Its New Colocation Facility in Hamburg</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>This is an excerpt from an article featured in ATMOsphere’s “Clean Cooling for Data Centers 2025” report, which can be downloaded here. ATMOsphere is the publisher of NaturalRefrigerants.com.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>46058</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>This is an excerpt from an article featured in ATMOsphere’s “Clean Cooling for Data Centers 2025” report, which can be downloaded here. ATMOsphere is the publisher of NaturalRefrigerants.com.
-In September 2023 Penta Infra broke ground on a new 4.4MW colocation facility in Hamburg located near the city’s airport. The Hamburg colocation facility opened in the first half of 2025 and boasts 2,500m2 (26,909ft2) of IT space.
-Six Secon air-cooled propane (R290) chillers were installed on the roof, each with a cooling capacity of 960kW (272TR) and a refrigerant charge of 38kg (84lbs) split across four separate refrigerant circuits. The water for the IT space is cooled to 20°C (68°F) and sent to computer room air-handlers, with the water returning to the chillers at a temperature of 32°C (89.6°F).
-The data center has been dubbed “Penta Infra HAM01” by Penta, with Ruben Uijtermerk, Mechanical Engineer at the company, stating that propane was chosen as a refrigerant because “it combines excellent thermodynamic efficiency with a very low GWP, providing high energy performance while maintaining environmental responsibility.”
-“Propane is particularly well-suited for medium-capacity applications like our Hamburg data center, offering reliable cooling performance with a proven safety record when installed with proper safety measures,” said Uijtermerk. “Secon’s extensive experience in implementing R290-based systems further ensures that safety and operational risks are minimized, adding confidence to this solution.”
-Read Part 1 Here
-Free cooling capabilities
-The chillers at the Penta Infra Hamburg data center feature a master–slave network, with two fully redundant and self-monitoring master controllers. They also come equipped with automatic transfer switches and uninterruptible power supplies for the controllers. Secon’s chillers include free cooling, but due to size limitations they cannot cover as much cooling capacity as the two dry coolers (there are plans to install two more). While separate units, the dry coolers are integrated into the chillers in terms of hydraulics and controls.
-Hamburg is located in northern Germany where summer temperatures range from 10 to 36°C (50 to 97°F), and winter temperatures range from −3 to 4°C (27 to 39°F). Thanks to the mild climate, the data center is able to use free cooling for a significant portion of the year. The power supply and control of the free coolers is managed by the chillers, which enables the full cooling capacity to be covered by free cooling. Pre-cooling mode starts at 27°C (80.6°F) and full free cooling is available from 16.5°C (61.7°F).
-“Up to 80% of the annual hours can be covered purely by free cooling,” Schadt said. “It’s a decisive factor in achieving a very low PUE value for the data center.”
-Pursuing a low PUE
-The PUE value for the facility is dictated by the German Energy Efficiency Act (EnEfG), which went into effect in November 2023 and requires all data centers with a connected load of 300kW or more to meet energy efficiency and waste heat requirements. Data centers commissioned before July 1, 2026, must have a PUE of ≤1.5 and a PUE of ≤1.3 by 2030.
-“We design according to the requirement in the EnEfG of an annual PUE of 1.2, meaning the hydrocarbon type chiller must be efficient enough to support this,” said Uijtermerk.
-The EnEfG also carries requirements to reuse waste heat, but as of 2025 there is no district heating network to connect to. Penta Infra HAM01 has two heat exchangers in the basement that enable it to connect to a district heating network, with the city and Penta Infra engaged in early discussions about a future district heating project.
-Uijtermerk said that in sites where district heating network connections are available, Penta sees “increased potential” in using reversible chillers, wherein heat is directly fed into the district heating network from the chiller; this would mitigate the need for dedicated heat pumps, increasing cost-effectiveness and maximizing the heat generating potential.
-Neither the EnEfG nor the EU F-gas Regulation broach the issues of HFOs or PFAS. However, Uijtermerk said that Penta more frequently sees natural refrigerants mentioned in client requests for information and requests for proposals.
-“There is increased awareness and appraisal by our clients for using natural refrigerants,” said Uijtermerk. “Penta believes that, if practically possible, hydrocarbons are the better choice over synthetic refrigerants.”</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/part-2-why-penta-infra-chose-secons-r290-chillers-for-its-new-colocation-facility-in-hamburg/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Part 1: BAC’s Heat Rejection and Single-Phase Immersion Technology Provide ‘End-to-End’ Cooling Solution for Data Centers</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>This is an excerpt from an article featured in ATMOsphere’s “Clean Cooling for Data Centers 2025” report, which can be downloaded here. ATMOsphere is the publisher of NaturalRefrigerants.com.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
+      <c r="C3" s="2" t="n">
         <v>46064</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>This is an excerpt from an article featured in ATMOsphere’s “Clean Cooling for Data Centers 2025” report, which can be downloaded here. ATMOsphere is the publisher of NaturalRefrigerants.com.
 BAC is a global manufacturer with more than 85 years of experience designing and producing heat rejection technology for the HVAC&amp;R industry. Headquartered in Jessup, Maryland, BAC serves a broad range of applications, including central air-conditioning, commercial and industrial refrigeration and process cooling.
@@ -1041,34 +541,343 @@
 “Our decades-long experience in large-scale central cooling systems allow us to provide guidance and customization that go beyond equipment,” Tysebaert said. BAC has supplied cooling systems to more than 1,000 data centers worldwide, delivering thousands of units annually to colocation facilities and edge sites.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>https://naturalrefrigerants.com/news/part-1-bacs-heat-rejection-and-single-phase-immersion-technology-provide-end-to-end-cooling-solution-for-data-centers/</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Johnson Controls Introduces Air-to-Water Reversible York YAS R290 Heat Pump Models to the European Market</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Johnson Controls is introducing its air-to-water reversible York-brand YAS propane (R290) heat pump models to the European market, offering configurations that can supply cooling, heating or simultaneous cooling and heating, and deliver up to 65/77°C (149/171°F) hot water, depending on the model.
+Using scroll compressor technology and axial fans, the three models ‒ YAS SC WP, YAS SC WP WA and YAS SC GPS ‒ operate in ambient temperatures as low as −20°C (−4°F). The units, which use 6.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Johnson Controls is introducing its air-to-water reversible York-brand YAS propane (R290) heat pump models to the European market, offering configurations that can supply cooling, heating or simultaneous cooling and heating, and deliver up to 65/77°C (149/171°F) hot water, depending on the model.
+Using scroll compressor technology and axial fans, the three models ‒ YAS SC WP, YAS SC WP WA and YAS SC GPS ‒ operate in ambient temperatures as low as −20°C (−4°F). The units, which use 6.1 or 8.1kg of propane, offer heating capacities ranging from 86.7 to 139kW (24.7 to 39.5TR) and cooling capacities from 66.3 to 110kW (18.9 to 31.3TR), supporting residential, commercial and industrial applications, according to Johnson Controls.
+“The scroll compressors with orbiting spirals are optimized for heat pump operation at high compression ratios,” Johnson Controls said. “Depending on the model, the [compressors] are arranged in tandem or trio configuration and paired with electronically controlled air flow on the source side, which enables excellent seasonal efficiency ratios.”
+Either/or units: Two of the YAS models produce heating or cooling, with one version optimized for colder climates and the other one for higher ambient temperature conditions.
+The YAS SC WP model for colder climates offers heating capacities from 88.9 to 112kW (25.3 to 31.8TR), with a SCOP of up to 4.29, and cooling capacities from 66.3 to 89.2kW (18.9 to 25.4TR), with an EER of up to 2.51.
+The wide ambient model YAS SC WP WA offers 88.2kW (25.1TR) of heating capacity, with a SCOP of up to 3.77, and 105kW (29.9TR) of cooling capacity, with an EER of up to 3.55.
+Simultaneous unit: The YAS SC GPS model offers three operation modes: cooling, heating or cooling with heating.
+When operating solely for chilling, the unit offers cooling capacities ranging from 72.1 to 99.1kW (20.5 to 28.2TR), with an EER of up to 2.73.
+When operating solely for heat, the unit offers heating capacities ranging from 86.7 to 116kW (24.7 to 33TR), with a COP of up to 3.92.
+In simultaneous mode, the unit offers cooling capacities ranging from 79.5 to 110kW (22.6 to 31.3TR) and heating capacities ranging from 101 to 139kW (28.7 to 39.5TR), with a total efficiency ratio of up to 8.68.
+Australian application: In 2024 Johnson Controls received compliance certification from the Queensland Resources, Safety and Health (RSH) statutory board for its York-brand YAS large-scale propane chillers and air-to-water heat pumps.
+Working with local officials, the manufacturer replaced the existing HFC air-conditioning unit in a Windsor shopping center with two roughly 300kW (85TR)-capacity R290 chillers, according to Rickey Du, Product and Technology Manager of Industrial Refrigeration at Johnson Controls for Australia and New Zealand.
+Installed in August 2024, the project became Queensland’s “first” approved propane chiller deployment, according to Du, with final regulatory approval granted in December 2024.
+Quotable: “Every unit is fully assembled and factory tested [and] supplied with the appropriate refrigerant and non-freezing oil charge,” Johnson Controls said. “As a result, installation only requires positioning the equipment and connecting it to the hydraulic and electrical supply lines.”
+“The scroll compressors with orbiting spirals are optimized for heat pump operation at high compression ratios.”
+Johnson Controls</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/johnson-controls-introduces-air-to-water-reversible-york-yas-r290-heat-pump-models-to-the-european-market/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Part 2: BAC’s Heat Rejection and Single-Phase Immersion Technology Provide ‘End-to-End’ Cooling Solution for Data Centers</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>This is an excerpt from an article featured in ATMOsphere’s “Clean Cooling for Data Centers 2025” report, which can be downloaded here. ATMOsphere is the publisher of NaturalRefrigerants.com.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>This is an excerpt from an article featured in ATMOsphere’s “Clean Cooling for Data Centers 2025” report, which can be downloaded here. ATMOsphere is the publisher of NaturalRefrigerants.com.
+BAC’s COBALT immersion cooling system can be found in action at Skybox Houston One, an HPC data center in Houston, Texas, with 4MW of installed IT power capacity. Operational since 2019,  the facility runs entirely on renewable energy and operates in 100% free-cooling mode year-round despite the notoriously hot and humid climate.
+The system features more than 300 26U-wide immersion tanks, each housing 13 high-density servers submerged in dielectric fluid. These tanks are connected to a closed-loop cooling water circuit served by six BAC evaporative cooling towers for heat rejection and five pump sets that circulate water between the tanks and towers. Within the data hall, four computer room air-conditioning (CRAC) units provide limited, non-mission-critical comfort cooling.
+The use of BAC’s immersion cooling technology substantially reduces the data center’s energy use compared to a setup using CRAHs (computer room air handlers) – which supply cool air to the server room via air-cooled chillers – according to Jan Tysebaert, Global General Manager for Data Center Cooling at BAC. IT power consumption was reduced by 20% as server fans were no longer required.
+Combined with the use of free evaporative cooling – rather than mechanical cooling – and a streamlined system architecture, total energy savings reached around 80% for the cooling system and approximately 30% at the overall facility level.
+The Skybox Houston One data center. Photo credit: Skybox
+PUE vs. TUE
+While most facilities report power usage effectiveness (PUE) as their primary efficiency metric, BAC also highlights total-power usage effectiveness (TUE), which is defined as the ratio of total facility load to compute load.
+“PUE looks at the facility, but it does not look at the efficiency of the IT hardware,” Tysebaert noted. “It does not do justice to liquid-cooled facilities.”
+PUE does not account for the effect of lowering IT load – such as by eliminating the need for server fans – and can therefore make a more efficient data center appear to have a higher PUE. For Skybox Houston One, the immersion and evaporative cooling configuration achieves a TUE of approximately 1.15 compared to 1.60 for a setup using air-cooled chillers and CRAHs.
+Beyond efficiency, the approach adopted at SkyBox Houston One is “extremely simple” in design, resulting in low upfront costs and enabling easy scaling, Tysebaert said. It can work with any type of server and at higher process fluid temperatures, he noted. By integrating the immersion tanks directly with the facility’s evaporative cooling system, BAC’s design also reduces the data hall footprint, enabling operators to maximize compute density within the same physical space.
+“It’s actually unbelievable [that] we’re not doing this for all other data centers worldwide already,” Tysebaert said.
+“PUE looks at the facility, but it does not look at the efficiency of the IT hardware,” Tysebaert noted. “It does not do justice to liquid-cooled facilities.”
+Jan Tysebaert, 
+Global General Manager for Data Center Cooling at BAC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/part-2-bacs-heat-rejection-and-single-phase-immersion-technology-provide-end-to-end-cooling-solution-for-data-centers/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EU Launches €1.8 Million Heat Pump Subscription Model for Leased Commercial and Public Buildings</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The EU has launched a €1.8 million ($2.15 million) subscription model, funded through its LIFE Program from November 2025 to October 2028, to encourage the adoption of heat pumps in leased commercial and public buildings.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>The EU has launched a €1.8 million ($2.15 million) subscription model, funded through its LIFE Program from November 2025 to October 2028, to encourage the adoption of heat pumps in leased commercial and public buildings.
+The HP-Subscribe model uses third-party ownership and subscription fees to address barriers to heat pump installations in leased buildings caused by the split incentive between landlords and tenants. Hydrocarbon natural refrigerant heat pumps are eligible under the EU LIFE Program and compliant with the EU F-gas Regulation’s low-GWP requirements.
+“With HP-Subscribe, we want to make clean heating accessible to every building, regardless of ownership structure or financial capacity,” said Petra Pomper, Project Coordinator and building sector expert at the Institute for European Energy and Climate Policy (IEECP). “This project demonstrates that the energy transition can advance in a way that is fair, scalable and effective.”
+Heat pumps offer a carbon-neutral alternative to fossil fuels for heating and cooling, aligning with goals outlined in the European Green Deal and the REPowerEU plan, according to the European Commission. In 2024 heat pumps claimed 28% of the region’s space heating market, according to the European Heat Pump Association (EHPA).
+Based on the size of the leased building, the required capacities for cooling, heating and hot water could range from a few kilowatts to more than a megawatt. In the past, landlords shouldered the financial burden of installing and maintaining heat pumps, while tenants paid lower energy bills.
+How HP-Subscribe works: The model shifts heat pump ownership, installation and maintenance to a service provider, a third party separate from the landlord or tenant. To spread the initial cost of the heat pump over time, end users pay a subscription fee.
+HP-Subscribe aims to engage energy-service companies, financial institutions, public authorities, building owners and manufacturers to validate and promote the model, with pilot projects in Austria, France and Greece, the European Commission said.
+In Ireland the project will connect existing heat pump initiatives with service providers and financial partners, according to EHPA.
+The project will enhance the business case for heat pumps by leveraging regulatory frameworks such as white certificate schemes and demand–response programs that support grid flexibility.
+Many options: Several European manufacturers offer propane (R290)-based heat pump solutions that meet the requirements of the model.
+Procure Plus appointed four R290 heat pumps produced by Viessmann Climate Solutions, a division EUof Carrier Global Corporation, to the U.K. social housing and other public sector low- and zero-carbon projects framework. The capacities of the units range from 1.1 to 140kW (0.6 to 39.8TR).
+Italian Enerblue’s Purple range of air-to-water heat pumps offers heating capacities of 22–221kW (6.3–62.8TR). Its new Palladium range includes a four-pipe model capable of providing simultaneous heating and cooling.
+In September 2025 Panasonic announced that it was investing €320 million ($373.8 million) to expand and refurbish its facility in the Czech Republic, with the aim of producing 1.4 million residential and commercial heat pumps for the European market by 2030.
+Cooling projects: The EU continues to finance the development of sustainable solutions as part of its climate action plan.
+The Life-ZeroGWP Project, coordinated by Italian Innova, developed the first high-efficiency double-ducted propane air conditioner without an outdoor unit. With less than 150g of R290 per circuit, the resulting INNOVA 2.0NR, available from 2022, compares to the best HFC solutions on the market in terms of energy efficiency and convenience, according to Life-ZeroGWP.
+The SMACool project, which runs until September 2027 with an allotted €3.9 million ($4.45 million) in funding, aims to develop a prototype of a residential air conditioner using elastocaloric technology. Instead of a refrigerant, it uses nickel-titanium, also known as nitinol, which heats up when mechanically stressed and cools when de-stressed.
+Quotable: “This subscription–based service guarantees modern, efficient and clean heating with reduced energy costs for tenants, while owners benefit from higher building value without the burden of capital investment,” EHPA said.
+“With HP-Subscribe, we want to make clean heating accessible to every building, regardless of ownership structure or financial capacity.”
+Petra Pomper, HP-Subscribe Project Coordinator</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/eu-launches-e1-8-million-heat-pump-subscription-model-for-leased-commercial-and-public-buildings/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HYTING Commissions ‘World’s First’ Customer-Installed Catalytic Hydrogen Air-Heating System</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HYTING, a German manufacturer of hydrogen-based heating solutions, has commissioned what it describes as the “world’s first” customer-installed catalytic hydrogen air-heating system in a new industrial facility in Offenbach, Germany.
+Paired with a heat pump, the 10kW (2.8TR) capacity catalytic unit supports the client’s peak heating demand, including in low ambient temperatures, using hydrogen supplied locally, according to HYTING.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HYTING, a German manufacturer of hydrogen-based heating solutions, has commissioned what it describes as the “world’s first” customer-installed catalytic hydrogen air-heating system in a new industrial facility in Offenbach, Germany.
+Paired with a heat pump, the 10kW (2.8TR) capacity catalytic unit supports the client’s peak heating demand, including in low ambient temperatures, using hydrogen supplied locally, according to HYTING. Flusys, a producer of pumps and fluid systems for industrial applications, installed the hybrid system to heat a 1,000m3 (35,300ft3) production space.
+The catalytic unit engages based on the hybrid setup’s optimum operating cost, HYTING told NaturalRefrigerants.com. The switch-on point depends on the heat pump’s efficiency and the relative cost of electricity versus the cost of hydrogen.
+“Our vision has always been to see hydrogen replace fossil fuels and make an invaluable contribution to decarbonizing the heating sector,” said Tim Hannig, Founder and Managing Director of HYTING. “Our technology is simple, safe, efficient and clean.”
+Applications for the catalytic hydrogen technology include commercial and industrial building HVAC, up to 300°C (572°F) process heating and auxiliary heating for the automotive sector, according to HYTING. Initially the units will come in heating capacities of 10 or 50kW (2.8 or 14.2TR), with higher capacity requirements met through modular configurations. HYTING, founded in 2021, said that it is scaling the unit for series production, with another customer installation scheduled for the first quarter of 2026.
+The technology: Rather than using flame-based combustion to generate heat, the process uses a catalytic chemical reaction. The technology produces no carbon emissions, nitrogen oxides or particulate matter, with water vapor as the only by-product.
+A controlled mixture of hydrogen and oxygen from the ambient air flows over HYTING’s proprietary catalyst surface, where it undergoes rapid oxidation, which generates heat.
+HYTING states that the unit is inherently safe, with hydrogen kept outside the catalyst zone in uncontrolled or hazardous concentrations.
+The technology, suitable for new installations and retrofits, can be combined with “any heat source,” the company said.
+Validation/certification: Durability testing, conducted by an independent engineering service provider, simulated 10 years of real-world operation, according to HYTING.
+The unit completed 2,500 hours of testing without failure or measurable wear on critical safety components.
+HYTING’s catalytic hydrogen technology is EU Gas Appliance Regulation-certified, indicating that it meets the safety, health and environmental requirements for gas-fired appliances.
+Optimizing systems: “Peak heating installations for commercial and industrial buildings can save customers costs from day one by drastically reducing capacity and demand charges and overall system costs,” HYTING said.
+Compared to installing a heat pump sized to meet peak demands, the hybrid setup can deliver up to 30% lower capital costs and up to 20% lower operating costs, depending on the price of hydrogen and the operating strategy, the company told NaturalRefrigerants.com.
+A simple retrofit solution can start around €20,000 ($23,600), HYTING said, with CAPEX costs based on project-specific requirements, including capacity and scope.
+Quotable: “The Flusys’ installation will prove not only the efficacy of HYTING’s technology but also demonstrate that hydrogen can replace natural gas as a cleaner, more sustainable source of heating,” the company said.
+“Our vision has always been to see hydrogen replace fossil fuels and make an invaluable contribution to decarbonizing the heating sector.”
+Tim Hannig, Founder and Managing Director of HYTING</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/hyting-commissions-worlds-first-customer-installed-catalytic-hydrogen-air-heating-system/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HVAC&amp;R Japan 2026: JEXSYS Launches 130°C High-Temperature Hot Water CO2 Heat Pump</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JEXSYS, formerly known as Nihon Netsugen Systems, has launched a high-temperature CO2 (R744) heat pump for the Asia–Pacific region capable of producing up to 130°C (266°F) pressurized hot water for industrial processing applications.
+The standard unit offers a heating capacity of 500kW (142.2TR) with a COP of 4.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>JEXSYS, formerly known as Nihon Netsugen Systems, has launched a high-temperature CO2 (R744) heat pump for the Asia–Pacific region capable of producing up to 130°C (266°F) pressurized hot water for industrial processing applications.
+The standard unit offers a heating capacity of 500kW (142.2TR) with a COP of 4.8. However, JEXSYS has the flexibility to manufacture larger capacities depending on a client’s needs, Katsuhiko Harada, the company’s President, told NaturalRefrigerants.com at the HVAC&amp;R Japan 2026 show. The event, held January 27‒30 in Tokyo, was organized by the The Japan Refrigeration and Air Conditioning Industry Association.
+“Our industrial refrigeration customers always have a boiler to meet the food and beverage industry’s requirement for 120‒130°C [248‒266°F] sanitary hot water,” Harada said. “Boilers cause a headache for two reasons: the price of fossil fuel is going up and really high CO2e emissions. Therefore, I think introducing a CO2 heat pump in the Japanese market is very important.”
+Development/reaction: To replace boilers in the food/beverage industry, JEXSYS first attempted to promote its ammonia (R717) heat pump. However, it did not meet the industry’s needs, with hot water temperatures topping out around 80‒90°C (176‒194°F), according to Harada.
+Drawing on its experience producing CO2 refrigeration equipment, JEXSYS spent a year developing a CO2 heat pump with the aim of producing 130°C pressurized hot water ‒ a goal it achieved at the end of 2025.
+The unit produces 4.2 metric tons of hot water per hour for industrial applications requiring temperatures above 100°C (212°F), including heating and melting of raw materials, sterilization, cleaning and drying.
+Although the main purpose of the unit is heating, it also produces cold water, according to Harada, making it eligible for the Japanese government’s subsidy schemes for heat recovery in the food industry.
+Gaining experience: JEXSYS launched its first CO2 condensing units in 2015, with early sales catered to small, privately owned cold storage companies.
+“So far we’ve installed 760 CO2 units in 240 completed projects,” Harada said, adding that the company’s docket for the next two years includes providing CO2 refrigeration units for “big” logistic centers owned by real estate-investing companies.
+It has CO2 equipment operating in Malaysia and the Philippines. Its five-year-old installation in Malaysia supplies fantastic energy savings with no reliability issues, Harada said.
+In 2023 the manufacturer opened a new factory in Shiga, Japan, which doubled its CO2 equipment-production capacity to meet the growing year-on-year demand.
+Business strategy: Looking ahead, Harada believes CO2 refrigeration and cooling will eventually mature and reach a growth ceiling, making it necessary for JEXSYS to develop a new business to sustain long-term growth.
+Entering the heating market with a CO2 heat pump aligns with the manufacturer’s growth strategy.
+“We expect this new business area to grow in the future, just as CO2 refrigeration has,” Harada said.
+Quotable: “We’ve been talking to several potential customers about a high-temperature CO2 heat pump for two or three years,” Harada said. “They are waiting for this launch,” he added, indicating that JEXSYS expects to sell 10 units in 2026.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/hvacr-japan-2026-jexsys-launches-130c-high-temperature-hot-water-co2-heat-pump/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cencosud, Nestlé and OXXO Colombia to Present at ATMO LATAM 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ATMOsphere, publisher of NaturalRefrigerants.com, has published a preview of the program for ATMOsphere (ATMO) LATAM 2026, which will feature a keynote from leading South America retailer Cencosud as well as presentations from Nestlé and OXXO Colombia, among other end users.
+Cencosud’s Sustainability Manager will kick off ATMO LATAM 2026, set for March 9–10 in Bogotá, by sharing the company’s vision for sustainability and its progress in adopting natural refrigerants.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ATMOsphere, publisher of NaturalRefrigerants.com, has published a preview of the program for ATMOsphere (ATMO) LATAM 2026, which will feature a keynote from leading South America retailer Cencosud as well as presentations from Nestlé and OXXO Colombia, among other end users.
+Cencosud’s Sustainability Manager will kick off ATMO LATAM 2026, set for March 9–10 in Bogotá, by sharing the company’s vision for sustainability and its progress in adopting natural refrigerants. The company operates more than 1,000 supermarkets and has made the “conversion of refrigerant gases” one of its sustainability priorities. It operates 15 stores that use transcritical CO2 (R744) refrigeration systems, according to its 2024 sustainability report.
+Nestlé and contractor Sistemas de Refrigeración Totales will present a critical load ammonia (R717) chiller with adiabatic condensers. OXXO Colombia, Latin America’s largest convenience store chain, will speak on the same panel about its work with natural refrigerants. 
+End users from the agricultural sector will also take the stage at ATMO LATAM 2026. Avo Pak, a Colombian avocado processor, will speak about its use of CO2 refrigeration systems. The joint presentation will also feature contractor SUTRAK and manufacturer Advansor. 
+Contractors and installers will have their own dedicated panel where they will share their experiences with natural refrigerants and outlook on the sector. Chilean contractor Sofrisur and Costa Rican contractor Dicoma Refrigeración are two of the confirmed presenters.
+Get Your Tickets to ATMO LATAM 2026
+Policy and training
+Day two will feature a policy panel covering standards and regulations impacting natural refrigerants in Latin America. It will feature Edwin M. Dickson, Environmental Consultant at Colombia’s Ministry of Environment and Sustainable Development, and Omarly Acevedo, International Consultant, Montreal Protocol and for UNIDO in Latin America. ATMOsphere will also discuss HFOs and the growing threat of PFAS (per- and polyfluoroalkyl substances) and TFA (trifluoroacetic acid).
+Training will also be a topic of discussion on day two of ATMO LATAM. ACAIRE (The Colombian Association of Air-Conditioning and Refrigeration), will headline the training panel with additional participants announced soon. The session will bring together experts to discuss the current state, opportunities and challenges of professional training in natural refrigerants in Latin America.
+The program is still being finalized and will also include sessions dedicated to global and regional market trends. Tickets for ATMO LATAM 2026 are still available and can be purchased here.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/cencosud-nestle-and-oxxo-colombia-to-present-at-atmo-latam-2026/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Advansor Launches ‘Enhanced’ CuBig II With 50% More Cooling and Heating Capacity</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Danish manufacturer Advansor, part of the Dover Corporation, has announced an “enhanced” version of its CO2 (R744)-based CuBig II that offers 50% more cooling and heating capacity.
+The CuBig II offers cooling, freezing, heating and air-conditioning all in one package, with the update pushing the unit’s medium-temperature (MT) capacity from 400 to 600kW (113 to 170TR) and its heating capacity from 650 to 850kW (184 to 241TR). In addition, Advansor said that the low-temperature (LT) performance has been optimized to “ensure stability under higher MT loads.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Danish manufacturer Advansor, part of the Dover Corporation, has announced an “enhanced” version of its CO2 (R744)-based CuBig II that offers 50% more cooling and heating capacity.
+The CuBig II offers cooling, freezing, heating and air-conditioning all in one package, with the update pushing the unit’s medium-temperature (MT) capacity from 400 to 600kW (113 to 170TR) and its heating capacity from 650 to 850kW (184 to 241TR). In addition, Advansor said that the low-temperature (LT) performance has been optimized to “ensure stability under higher MT loads.”
+“The LT capacity no longer drops as aggressively, which means improved simultaneous cooling for MT and LT circuits,” said Kenneth Madsen, CTO of Advansor, in a press release. “The wider operating envelope supports more diverse load combinations, reducing design constraints and improving adaptability.”
+The CuBig II is designed for large supermarkets and cold storage facilities and is also “ideal” as a heat pump for commercial and industrial applications, according to Advansor.
+Additional details: The CuBig II has a maximum low-temperature capacity of 330kW (93TR), a maximum air-conditioning capacity of 180kW (51TR) and a maximum heat recovery capacity of 850kW.
+Product evolutions: In addition to the CuBig II update, Advansor has also released new versions of its CO2-based ValuePack and Steel XL rack in the past year.
+Advansor launched a new version of its SteelXL rack in January 2025 with a maximum cooling capacity of 2.7MW (767TR), 1.9MW (540TR) of freezing, up to 4MW (1,137TR) of heating and 0.5MW (142TR) of air-conditioning, all on one frame.
+That same month the company launched an upgrade of its ValuePack refrigeration unit, raising the standard operating pressure to 130bar (1,885psi) from 120bar (1,740psi). The enhancement was designed to facilitate higher cooling capacities and improve operational efficiency and safety, according to Advansor, while also enabling the unit to be used for cold storage and light industrial applications, in addition to food retail.
+Quotable: “The larger capacity range often correlates with optimized compressor staging and reduced energy consumption per kW delivered,” said Madsen. “All of this gives our customers greater flexibility and performance.”</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/advansor-launches-enhanced-cubig-ii-with-50-more-cooling-and-heating-capacity/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Guide to Working with Propane Available in English</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>The textbook Propane, Naturally Safe, published last year in Norwegian and German, is now available in an English-language edition.
 Authored by refrigeration experts Stig Rath and Harald Erös, the book is described as a best-practice guide for heat pumps and refrigeration systems using propane (R290) and other A3 (flammable) refrigerants in commercial, industrial and residential buildings. Rath and Erös also collaborated on the German edition, while Rath wrote the Norwegian version.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>46063</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>The textbook Propane, Naturally Safe, published last year in Norwegian and German, is now available in an English-language edition.
 Authored by refrigeration experts Stig Rath and Harald Erös, the book is described as a best-practice guide for heat pumps and refrigeration systems using propane (R290) and other A3 (flammable) refrigerants in commercial, industrial and residential buildings. Rath and Erös also collaborated on the German edition, while Rath wrote the Norwegian version.
@@ -1105,78 +914,32 @@
 The Environmental Investigation Agency (EIA) US said in a report last October that it supports full harmonization of U.S. standards on the use of A3 hydrocarbon refrigerants in HVAC equipment with the global standard IEC 60335-2-40. This could enable 78–88% of new air-conditioning and heat-pump equipment in the U.S. to transition to propane (R290) between 2030 and 2035, according to the EIA.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://naturalrefrigerants.com/news/guide-to-working-with-propane-available-in-english/</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Trade Groups Appeal New York Court Decision Rejecting Effort to Stop HFC Regs</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>The Air-Conditioning, Heating, and Refrigeration Institute (AHRI) and Heating Air-Conditioning Refrigeration Distributors International (HARDI) have appealed a court decision in December rejecting their action to void updated New York State regulations on HFC emissions.
-The December decision came from the New York State Supreme Court, County of Albany, in a case brought by AHRI and HARDI against the New York State Department of Environmental Conservation (NYSDEC). AHRI and HARDI on January 20 filed a notice of appeal with the Appellate Division of the New York State Supreme Court, Third Judicial Department.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>California Grant of $1.5 Million to Fund Research on Risk of Propane in Outdoor Heat Pumps</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Air-Conditioning, Heating, and Refrigeration Technology Institute (AHRTI), the research arm of the AHRI, has been awarded a $1.5 million (€1.26 million) grant to support “essential research on the risk assessment” of residential monobloc air-to-water heat pumps (ATWHPs) using higher charges of A3 (flammable) refrigerants in North America, according to an announcement from AHRI on LinkedIn.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>46070</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>The Air-Conditioning, Heating, and Refrigeration Institute (AHRI) and Heating Air-Conditioning Refrigeration Distributors International (HARDI) have appealed a court decision in December rejecting their action to void updated New York State regulations on HFC emissions.
-The December decision came from the New York State Supreme Court, County of Albany, in a case brought by AHRI and HARDI against the New York State Department of Environmental Conservation (NYSDEC). AHRI and HARDI on January 20 filed a notice of appeal with the Appellate Division of the New York State Supreme Court, Third Judicial Department.
-The trade groups filed their original suit in April 2025  seeking declaratory judgment and voidance of the amended 6 NYCRR Part 494 regulations, which impose restrictions on the HFC refrigerants used in air conditioners, heat pumps, refrigeration and water heaters.
-The regulations include 20-year GWP limits of 10 for many new HVAC&amp;R systems starting in 2034, thereby helping to foster the adoption of natural refrigerant-based applications. Beginning in 2026, new supermarket and cold-storage systems with refrigerant charge capacity of 50lbs (23kg) or greater are prohibited from using refrigerants with a GWP20 greater than 580. The rules also include prohibitions on bulk virgin refrigerants and containers and a variance process.
-In their appeal, the AHRI and HARDI are requesting that the lower court’s decision be reversed, stating that New York State did not follow proper administrative procedure when enacting the restrictions in the amended Part 494 regulations. The trade groups continue to argue for full annulment of the regulations “due to concerns regarding enforcement, cost and the availability of compliant refrigerant,” they said in a statement announcing the appeal.
-In the filing, AHRI and HARDI call for a review of whether the state took market factors into account, specifically referencing provisions that call for a ban of bulk regulated substances, a ban on regulated substances with a global warming potential greater than 10, or 20 in some cases, and the further regulation of residential HVAC equipment.
-“AHRI opposes this ruling, which, if left in place, would greatly burden both consumers and manufacturers,” said AHRI President and CEO Stephen Yurek.
-“Part 494 sets mandates the market cannot meet,” said HARDI CEO Talbot Gee.
-Not arbitrary and capricious
-In the December decision rejecting the trade groups’ original suit, Justice Richard J. McNally, Jr., found that “DEC’s adoption of amended Part 494 was not arbitrary and capricious, DEC complied with the State Administrative Procedure Act, and DEC did not act in excess of its jurisdiction.” In addition, McNally noted that amended Part 494 “includes a variance process which permits entities, including small businesses, to apply for temporary relief from certain requirements if the entity cannot comply.”
-The NYSDEC did not respond to a request for a comment for this article, but it stated in 2024 that the updated HFC rules were designed to help implement New York’s Climate Leadership and Community Protection Act (CLCPA), which requires the state to reduce greenhouse gas emissions from 1990 levels by 40% by 2030 and by 85% by 2050, achieving net-zero emissions by 2050. Notably, the rules do not require the replacement of existing equipment prior to the end of its useful life – a major concern among food retailers who opposed the new regulations.
-New York’s amended HFC regulations are among the most ambitious in the U.S., surpassing in some respects the U.S. AIM Act implemented by the U.S. Environmental Protection Agency (EPA). The Technology Transitions Rule under the AIM Act is currently undergoing reconsideration by the EPA.
-New York is part of the U.S. Climate Alliance, a bipartisan coalition of 24 governors that has recommitted itself to protecting the climate in the face of regulatory rollbacks by the EPA. Other states with proactive HFC regulations include California and Washington. New York, unlike the EPA or other states, uses a 20-year GWP (GWP20) value for gases rather than the traditional 100-year GWP (GWP100) value. (Some of the New York regulations refer to federal rules that use GWP100.)
-New York regulators will be speaking about HFC regulations and related matters at the ATMOsphere America Summit 2026, scheduled for June 2–3 in the New York City area. ATMOsphere America is organized by ATMOsphere, publisher of NaturalRefrigerants.com.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://naturalrefrigerants.com/news/trade-groups-appeal-new-york-court-decision-rejecting-effort-to-stop-hfc-regs/</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Natural Refrigerants</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>California Grant of $1.5 Million to Fund Research on Risk of Propane in Outdoor Heat Pumps</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The Air-Conditioning, Heating, and Refrigeration Technology Institute (AHRTI), the research arm of the AHRI, has been awarded a $1.5 million (€1.26 million) grant to support “essential research on the risk assessment” of residential monobloc air-to-water heat pumps (ATWHPs) using higher charges of A3 (flammable) refrigerants in North America, according to an announcement from AHRI on LinkedIn.</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>46070</v>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>The Air-Conditioning, Heating, and Refrigeration Technology Institute (AHRTI), the research arm of the AHRI, has been awarded a $1.5 million (€1.26 million) grant to support “essential research on the risk assessment” of residential monobloc air-to-water heat pumps (ATWHPs) using higher charges of A3 (flammable) refrigerants in North America, according to an announcement from AHRI on LinkedIn.
 The grant comes from the North American Sustainable Refrigeration Council (NASRC) through its F-gas Reduction Incentive Program (FRIP), which is funded by the California Air Resources Board (CARB). It makes up for funding that had been expected from the U.S. Department of Energy (DOE) but was delayed. Last September NASRC solicited proposals from qualified third-party subcontractors to conduct this risk assessment.
@@ -1196,9 +959,229 @@
 The U.S. branch of the Environmental Investigation Agency (EIA) said in a 2025 report that it supports full harmonization of U.S. standards on the use of hydrocarbon refrigerants in HVAC equipment with the global standard IEC 60335-2-40. This could enable 78–88% of new air-conditioning and heat-pump equipment in the U.S. to transition to propane between 2030 and 2035, according to the EIA.</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/california-grant-of-1-5-million-to-fund-research-on-risk-of-propane-in-outdoor-heat-pumps/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Flow Environmental Services, St. Paul Local 455 Team Up for CO2 Heat-Pump Training and Demonstrations</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>In conjunction with Minnesota’s initiative to develop a clean-energy hub, Rogers, Minnesota (U.S.), manufacturer Flow Environmental Services and the St.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In conjunction with Minnesota’s initiative to develop a clean-energy hub, Rogers, Minnesota (U.S.), manufacturer Flow Environmental Services and the St. Paul Steamfitters/Pipefitters Union (Local 455) have teamed up to deliver hands-on CO2 (R744) heat-pump training and demonstrations.
+Grid Catalyst, a Minneapolis energy technology accelerator and facilitator, coordinated the project, which included public/private funding through the Minnesota Energy Alley initiative. The ANSWR CO2 heat pump, manufactured and installed by Flow, meets the 100,000ft2 (9,290m2) union facility’s base cooling/heating load through the building’s existing HVAC and hydronic system, Grid Catalyst told NaturalRefrigerants.com. The design also offers versatile training configurations, with connections to geothermal and outdoor air heat sources.
+“We’re not only running our own building’s heating and cooling on the ANSWR heat pump, but we’re building a living lab our apprentices can train on every day,” said Jeremy McConkey, Training Director at Local 455.
+Grid Catalyst indicated that a third-party measurement and verification study, conducted with engineering and utility partners, will validate the CO2 heat pump’s performance, with results expected in 2027.
+Sean Jarvie, Flow Environmental Systems’ CTO, highlights the CO2 heat pump installation at the St. Paul Steamfitters/Pipefitters Union (Local 455) as part of the grand opening ceremonies. Photo credit: Grid Catalyst.
+The opportunities: “This site will be open for nationwide training and demonstrations, with a strong emphasis on CO2 refrigeration for high-, medium- and low-temperature applications,” Grid Catalyst said.
+To support the adoption of the technology, Local 455 maintains an open-door policy, showcasing the CO2 heat pump to engineers, owners, policymakers, utility providers and the greater community.
+Local 455 provides “cutting-edge” technology training for commercial and industrial refrigeration, geothermal, HVAC, hot-water heating, steam and controls, according to Grid Catalyst. With Flow’s expertise, the manufacturer will work with the union to create a new training program for the CO2 heat pump.
+“Having this technology installed and operating at the Local 455 training center means the next generation of HVAC technicians will come trained on CO2 systems,” said Sean Jarvie, Flow Environmental Systems’ CTO. “That’s how you change an industry.”
+The benefits: The ANSWR heat pump, capable of simultaneously providing cooling, heating and domestic hot water, replaces traditionally separate systems to cut upfront costs and provide efficiency gains, according to Flow.
+The unit offers several configurations, including air source, water source, geothermal, heat recovery chiller/boiler or a hybrid of all these options.
+The modular unit operates in ambient temperatures ranging from −40 to 120°F (−40 to 49°C), supplying domestic hot water at 180°F (82°C), heating from 90 to 180°F (32 to 82°C) and cooling from 0 to 75°F (−18 to 24°C).
+Through the Local 455 installation, Flow will gather real-world data to confirm that the ANSWR system performs reliably in North America’s coldest climates, with winter temperatures dropping as low as −40°F.
+Growing market: Flow expects significant sales growth in 2026, the company told NaturalRefrigerants.com. It added that in January alone, it received more commitments to purchase ANSWR CO2 heat pumps than in the previous 12 months.
+Flow, along with Ambient Enterprises and Gil-Bar Industries, was named runner-up in New York’s Empire Technology Prize competition for developing, manufacturing and installing high-temperature CO2-based heat pumps for a range of commercial applications.
+The company reports that in 2025 it opened a decarbonization training center in San Jose, California, and provided CO2 equipment for multiple applications, including airports, hospitality, multi-family units, offices, universities and more.
+Quotable: “The biggest barrier to alternative refrigerant adoption isn’t the technology ‒ it’s the lack of real-world proof points,” said Nina Axelson, President of Grid Catalyst. “That’s exactly what pilot installations like this one create. When a union training center is using a CO2 heat pump as both a main source of heating and cooling as well as a teaching tool for future installers, you are moving the needle from ’emerging technology’ to ‘industry standard in the making.'”
+“This site will be open for nationwide training and demonstrations, with a strong emphasis on CO2 refrigeration for high-, medium- and low-temperature applications.” 
+Grid Catalyst</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/minnesota-flow-environmental-services-st-paul-local-455-team-up-for-co2-heat-pump-training-and-demonstrations/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trade Groups Appeal New York Court Decision Rejecting Effort to Stop HFC Regs</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Air-Conditioning, Heating, and Refrigeration Institute (AHRI) and Heating Air-Conditioning Refrigeration Distributors International (HARDI) have appealed a court decision in December rejecting their action to void updated New York State regulations on HFC emissions.
+The December decision came from the New York State Supreme Court, County of Albany, in a case brought by AHRI and HARDI against the New York State Department of Environmental Conservation (NYSDEC). AHRI and HARDI on January 20 filed a notice of appeal with the Appellate Division of the New York State Supreme Court, Third Judicial Department.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>The Air-Conditioning, Heating, and Refrigeration Institute (AHRI) and Heating Air-Conditioning Refrigeration Distributors International (HARDI) have appealed a court decision in December rejecting their action to void updated New York State regulations on HFC emissions.
+The December decision came from the New York State Supreme Court, County of Albany, in a case brought by AHRI and HARDI against the New York State Department of Environmental Conservation (NYSDEC). AHRI and HARDI on January 20 filed a notice of appeal with the Appellate Division of the New York State Supreme Court, Third Judicial Department.
+The trade groups filed their original suit in April 2025  seeking declaratory judgment and voidance of the amended 6 NYCRR Part 494 regulations, which impose restrictions on the HFC refrigerants used in air conditioners, heat pumps, refrigeration and water heaters.
+The regulations include 20-year GWP limits of 10 for many new HVAC&amp;R systems starting in 2034, thereby helping to foster the adoption of natural refrigerant-based applications. Beginning in 2026, new supermarket and cold-storage systems with refrigerant charge capacity of 50lbs (23kg) or greater are prohibited from using refrigerants with a GWP20 greater than 580. The rules also include prohibitions on bulk virgin refrigerants and containers and a variance process.
+In their appeal, the AHRI and HARDI are requesting that the lower court’s decision be reversed, stating that New York State did not follow proper administrative procedure when enacting the restrictions in the amended Part 494 regulations. The trade groups continue to argue for full annulment of the regulations “due to concerns regarding enforcement, cost and the availability of compliant refrigerant,” they said in a statement announcing the appeal.
+In the filing, AHRI and HARDI call for a review of whether the state took market factors into account, specifically referencing provisions that call for a ban of bulk regulated substances, a ban on regulated substances with a global warming potential greater than 10, or 20 in some cases, and the further regulation of residential HVAC equipment.
+“AHRI opposes this ruling, which, if left in place, would greatly burden both consumers and manufacturers,” said AHRI President and CEO Stephen Yurek.
+“Part 494 sets mandates the market cannot meet,” said HARDI CEO Talbot Gee.
+Not arbitrary and capricious
+In the December decision rejecting the trade groups’ original suit, Justice Richard J. McNally, Jr., found that “DEC’s adoption of amended Part 494 was not arbitrary and capricious, DEC complied with the State Administrative Procedure Act, and DEC did not act in excess of its jurisdiction.” In addition, McNally noted that amended Part 494 “includes a variance process which permits entities, including small businesses, to apply for temporary relief from certain requirements if the entity cannot comply.”
+The NYSDEC did not respond to a request for a comment for this article, but it stated in 2024 that the updated HFC rules were designed to help implement New York’s Climate Leadership and Community Protection Act (CLCPA), which requires the state to reduce greenhouse gas emissions from 1990 levels by 40% by 2030 and by 85% by 2050, achieving net-zero emissions by 2050. Notably, the rules do not require the replacement of existing equipment prior to the end of its useful life – a major concern among food retailers who opposed the new regulations.
+New York’s amended HFC regulations are among the most ambitious in the U.S., surpassing in some respects the U.S. AIM Act implemented by the U.S. Environmental Protection Agency (EPA). The Technology Transitions Rule under the AIM Act is currently undergoing reconsideration by the EPA.
+New York is part of the U.S. Climate Alliance, a bipartisan coalition of 24 governors that has recommitted itself to protecting the climate in the face of regulatory rollbacks by the EPA. Other states with proactive HFC regulations include California and Washington. New York, unlike the EPA or other states, uses a 20-year GWP (GWP20) value for gases rather than the traditional 100-year GWP (GWP100) value. (Some of the New York regulations refer to federal rules that use GWP100.)
+New York regulators will be speaking about HFC regulations and related matters at the ATMOsphere America Summit 2026, scheduled for June 2–3 in the New York City area. ATMOsphere America is organized by ATMOsphere, publisher of NaturalRefrigerants.com.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/trade-groups-appeal-new-york-court-decision-rejecting-effort-to-stop-hfc-regs/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Epta Completes Its Acquisition of Hauser</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Epta announced on February 17 that it has completed its acquisition of Hauser, with the deal increasing the Epta Group’s revenues to more than €2 billion ($2.3 billion) annually and its headcount to more than 10,000 employees.
+The multinational manufacturer of commercial refrigeration equipment announced its acquisition of Hauser, an Austrian manufacturer of self-contained and remote refrigeration cabinets and industrial refrigeration systems, in July 2025.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Epta announced on February 17 that it has completed its acquisition of Hauser, with the deal increasing the Epta Group’s revenues to more than €2 billion ($2.3 billion) annually and its headcount to more than 10,000 employees.
+The multinational manufacturer of commercial refrigeration equipment announced its acquisition of Hauser, an Austrian manufacturer of self-contained and remote refrigeration cabinets and industrial refrigeration systems, in July 2025. It said at the time that the goal of the deal is “to enhance [the] Epta Group’s presence and competitiveness in the retail sector.” Hauser operates two plants, one in Austria and one in the Czech Republic.
+“This operation marks a key milestone in Epta’s long-term strategy,” said Marco Nocivelli, CEO of Epta, in a press release. “By combining competencies, technologies and scale, we significantly enhance our ability to drive sustainable and digital innovation. The acquisition of Hauser further strengthens our offering along the full value chain and consolidates our leadership in natural refrigeration and energy-efficient solutions.”
+Epta and Hauser both manufacture commercial refrigeration equipment, including plug-in propane (R290) cases, remote CO2 (R744) cases and CO2 racks. Hauser also manufactures industrial refrigeration systems using CO2, ammonia (R717) and synthetic refrigerants.
+“Joining Epta marks a pivotal moment for our company,” said Thomas Loibl, CEO of Hauser, in a press release. “With a global partner that shares our core values, Hauser is well positioned to further consolidate its footprint while continuing to deliver long- term value to customers.”
+Epta told NaturalRefrigerants.com in July 2025 that it is “actively evaluating further expansion opportunities,” specifically new acquisitions/partnerships in Asia and North America.
+“The acquisition of Hauser further strengthens our offering along the full value chain and consolidates our leadership in natural refrigeration and energy-efficient solutions.”
+Marco Nocivelli, 
+CEO of Epta</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/epta-completes-its-acquisition-of-hauser/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BOCK CO2 Compressors Found to Vibrate Less at Ohio Supermarket</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>In a new whitepaper, Danish component manufacturer Danfoss reported that its BOCK HGX series CO2 (R744) compressors experienced an average of 83% less vibration compared to legacy compressors in a test retrofit installation at a supermarket in Ohio.
+The whitepaper – “Danfoss BOCK CO₂ Compressor Reduces Vibration for Optimal Transcritical Supermarket Refrigeration Performance” – is available here.
+Using a calibrated vibration meter, Danfoss application engineers captured measurements at multiple locations on the rack and at various points on individual compressors and common piping lines.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In a new whitepaper, Danish component manufacturer Danfoss reported that its BOCK HGX series CO2 (R744) compressors experienced an average of 83% less vibration compared to legacy compressors in a test retrofit installation at a supermarket in Ohio.
+The whitepaper – “Danfoss BOCK CO₂ Compressor Reduces Vibration for Optimal Transcritical Supermarket Refrigeration Performance” – is available here.
+Using a calibrated vibration meter, Danfoss application engineers captured measurements at multiple locations on the rack and at various points on individual compressors and common piping lines.
+Compared to existing CO2 compressors, the BOCK units achieved vibration reductions ranging from 48.3% to 97.7% at various points and capacities, the whitepaper said.
+In addition, the BOCK lead compressor employing a variable frequency drive (VFD) achieved a wider frequency range – from 35–70Hz compared to the original compressor’s 40-60Hz range – resulting in a larger capacity range in the suction group without added vibration,” it said.
+Abnormal vibration
+The Ohio supermarket had been experiencing “abnormal, excessive compressor and rack vibration” in its legacy transcritical CO2 system, said the whitepaper. It added that excessive vibration is “one of the most persistent CO2 compressor reliability challenges,” causing damage to racks, piping and structural components and resulting in reduced compression cycle effectiveness and excess energy consumption.
+“We are encouraged by the test results that affirmed the operational and sustainability benefits of BOCK compressors for transcritical CO2 refrigeration systems,” said Chris Brown, Application Engineering Manager at Danfoss, in a statement. “Danfoss BOCK HGX compressors can deliver the energy savings and environmental benefits of CO2 safely and reliably in a wide range of supermarket refrigeration sites, removing a critical barrier to increased adoption of CO2 across the industry.”
+“We are encouraged by the test results that affirmed the operational and sustainability benefits of BOCK compressors for transcritical CO2 refrigeration systems.”
+Chris Brown, Danfoss
+In the test case, seven Danfoss BOCK HGX series compressors were employed in a transcritical system. All compressors were semi-hermetic and were charged with a synthetic refrigeration oil based on special polyolesters for use with CO2 in transcritical applications. The refrigeration rack supplied a total of 1,121kBTUh (93.4TR/328,5kW) of cooling.
+“The vibration reductions also resulted in less noise and less shaking of the pipes and other rack components,” Danfoss said. “In addition to the improvements in safety and reliability of the operating components, the environment of the area was much more pleasant for maintenance personnel.”
+Danfoss’s BOCK HGX56 CO2T six-cylinder semi-hermetic compressor was named the winner in the refrigeration category of the 2025 AHR Expo Innovation Award.
+Danfoss finalized its acquisition of CO2 compressor manufacturer BOCK from NORD Holding in March 2023.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://naturalrefrigerants.com/news/bock-co2-compressors-found-to-vibrate-less-at-ohio-supermarket/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Natural Refrigerants</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Copeland’s Medium-Temp Scroll Compressor Seen as Expanding CO2 Market in North America</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Copeland’s new medium-temperature transcritical CO2 (R744) scroll compressor facilitates the development of smaller, distributed CO2 racks and condensing units that could expand the range of end users employing CO2 refrigeration, including convenience stores.
+“It gives system designers the flexibility to reduce the footprint of their distributed equipment,” said Andre Patenaude, Director, Solution Strategy for Copeland, a U.S.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Copeland’s new medium-temperature transcritical CO2 (R744) scroll compressor facilitates the development of smaller, distributed CO2 racks and condensing units that could expand the range of end users employing CO2 refrigeration, including convenience stores.
+“It gives system designers the flexibility to reduce the footprint of their distributed equipment,” said Andre Patenaude, Director, Solution Strategy for Copeland, a U.S.-based component manufacturer. Patenaude shared these remarks on February 11 at a natural refrigerants training event in Poughkeepsie, New York, hosted by the North American Sustainable Refrigeration Council (NASRC).
+“Every manufacturer can make smaller CO2 racks now, and it opens the door for CO2 condensing units in the capacity ranges that these compressors provide,” he added. Those capacities range between 15,000 to 130,000BTUs (1.25 and 10.8TR/4.4 and 38kW).
+Copeland’s ZTI CO₂ transcritical medium-temperature scroll compressor. Photo credit: Copeland
+Copeland has manufactured a low-temperature subcritical CO2 scroll compressor globally for about 15 years. In Europe, the company introduced a medium-temperature CO2 transcritical scroll compressor in 2021, followed by a CO2 outdoor condensing unit line with scroll compressors for the European market in May of 2025.
+In North America, Copeland announced the launch of the medium-temperature transcritical CO2 scroll compressor in December. In February, this compressor made Copeland the winner of the 2026 AHR Expo (International Air-Conditioning, Heating, Refrigerating Exposition) Innovation Award in the refrigeration category.
+Remodeling option
+In addition to being suited for smaller supermarkets and convenience stores, the new medium-temperature scroll compressors can help conventional supermarkets with partial remodeling. “They might not want to rip and replace everything in their store, but they’ve got a lineup of cases that are old,” said Patenaude. “They can do a CO2 lineup with some low temp, some medium temp, in a small-footprint piece of equipment that the scrolls enable.”
+The scrolls also allow conventional stores to install several small CO2 racks or condensing units in a distributed architecture rather than in a single centralized rack in a machine room, noted Patenaude.
+“It gives system designers the flexibility to reduce the footprint of their distributed equipment.”
+Andre Patenaude, Copeland
+The new medium-temperature CO2 scroll compressors also feature a brushless permanent magnet (BPM) motor instead of an induction motor, which is limited in speed. The BPM motor’s speed ranges from 20 to 90Hz (1,200 to 5,400rpm). “Designers now have a really wide range of capacity modulation,” said Patenaude. The compressors are also available in fixed speed.
+The new scroll compressor offers dynamic vapor injection (DVI), a process that allows high-pressure refrigerant gas to be digested through the compression cycle, eliminating the need for parallel compression, said Copeland.
+At the NASRC training event, Copeland exhibited a transcritical CO2 rack with a low-temperature scroll compressor and a medium-temperature semi-hermetic reciprocating compressor. The new medium-temperature scroll could replace the reciprocating compressor.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://naturalrefrigerants.com/news/california-grant-of-1-5-million-to-fund-research-on-risk-of-propane-in-outdoor-heat-pumps/</t>
+          <t>https://naturalrefrigerants.com/news/copelands-medium-temp-scroll-compressor-seen-as-expanding-co2-market-in-north-america/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1206,7 +1189,6 @@
           <t>Natural Refrigerants</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1221,7 +1203,7 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46071</v>
+        <v>46077.64725694444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1239,7 +1221,6 @@
           <t>Trane Technologies</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1254,7 +1235,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46063</v>
+        <v>46077.64726851852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1272,7 +1253,6 @@
           <t>Trane Technologies</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1303,7 +1283,6 @@
           <t>Trane Technologies</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1318,7 +1297,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46059</v>
+        <v>46077.64729166667</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1336,7 +1315,6 @@
           <t>Trane Technologies</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1351,7 +1329,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46059</v>
+        <v>46077.64729166667</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1369,7 +1347,6 @@
           <t>Trane Technologies</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1384,7 +1361,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46057</v>
+        <v>46077.64730324074</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1402,7 +1379,6 @@
           <t>Trane Technologies</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
